--- a/SensitivityAnalysis/LeaveOneOut/Metaanalysis/loo.xlsx
+++ b/SensitivityAnalysis/LeaveOneOut/Metaanalysis/loo.xlsx
@@ -6,13 +6,13 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="ebi-a-GCST006979" r:id="rId3" sheetId="1"/>
-    <sheet name="ebi-a-GCST005194" r:id="rId4" sheetId="2"/>
-    <sheet name="HF" r:id="rId5" sheetId="3"/>
-    <sheet name="IS" r:id="rId6" sheetId="4"/>
-    <sheet name="ukb-b-14057" r:id="rId7" sheetId="5"/>
-    <sheet name="ebi-a-GCST011365" r:id="rId8" sheetId="6"/>
-    <sheet name="ebi-a-GCST006867" r:id="rId9" sheetId="7"/>
+    <sheet name="Heel bone mineral density" r:id="rId3" sheetId="1"/>
+    <sheet name="Sheet1" r:id="rId4" sheetId="2"/>
+    <sheet name="Coronary artery disease" r:id="rId5" sheetId="3"/>
+    <sheet name="Myocardial infarction" r:id="rId6" sheetId="4"/>
+    <sheet name="Sheet4" r:id="rId7" sheetId="5"/>
+    <sheet name="Non-cancer illness code, self-r" r:id="rId8" sheetId="6"/>
+    <sheet name="Type 2 diabetes" r:id="rId9" sheetId="7"/>
   </sheets>
 </workbook>
 </file>
@@ -26,10 +26,10 @@
     <t>Estimate</t>
   </si>
   <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>C2</t>
+    <t>CI_LOW</t>
+  </si>
+  <si>
+    <t>CI_HIGH</t>
   </si>
   <si>
     <t>SE</t>
@@ -346,19 +346,19 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2214099332546395</v>
+        <v>-1.4015776287277675</v>
       </c>
       <c r="D2" t="n">
-        <v>0.14311121866777887</v>
+        <v>-1.7501238596949888</v>
       </c>
       <c r="E2" t="n">
-        <v>0.29970864784150014</v>
+        <v>-1.053031397760546</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03994832376880646</v>
+        <v>0.17782970967715372</v>
       </c>
       <c r="G2" t="n">
-        <v>2.983391364305828E-8</v>
+        <v>3.232882036189485E-15</v>
       </c>
     </row>
     <row r="3">
@@ -369,19 +369,19 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2822261088617243</v>
+        <v>-1.6807401761764733</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2081560068028972</v>
+        <v>-1.8861650794791411</v>
       </c>
       <c r="E3" t="n">
-        <v>0.35629621092055136</v>
+        <v>-1.4753152728738055</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03779086839736076</v>
+        <v>0.10480862413401414</v>
       </c>
       <c r="G3" t="n">
-        <v>8.135896837267723E-14</v>
+        <v>7.130217619944625E-58</v>
       </c>
     </row>
     <row r="4">
@@ -392,19 +392,19 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2749365150111475</v>
+        <v>-1.6583639765829643</v>
       </c>
       <c r="D4" t="n">
-        <v>0.15602066499540998</v>
+        <v>-2.16711594055027</v>
       </c>
       <c r="E4" t="n">
-        <v>0.39385236502688503</v>
+        <v>-1.1496120126156586</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06067135204884568</v>
+        <v>0.25956732855474784</v>
       </c>
       <c r="G4" t="n">
-        <v>5.8546764648028096E-6</v>
+        <v>1.6702321788434132E-10</v>
       </c>
     </row>
     <row r="5">
@@ -415,19 +415,19 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>0.15467793989100037</v>
+        <v>-1.1362689954192724</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07693060340991685</v>
+        <v>-1.4682843772107375</v>
       </c>
       <c r="E5" t="n">
-        <v>0.23242527637208388</v>
+        <v>-0.8042536136278073</v>
       </c>
       <c r="F5" t="n">
-        <v>0.039667008408716085</v>
+        <v>0.1693956029548291</v>
       </c>
       <c r="G5" t="n">
-        <v>9.64272646407781E-5</v>
+        <v>1.9760308667197576E-11</v>
       </c>
     </row>
     <row r="6">
@@ -438,19 +438,19 @@
         <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2218264079630959</v>
+        <v>-1.4001473703893499</v>
       </c>
       <c r="D6" t="n">
-        <v>0.13435785634265993</v>
+        <v>-1.787552146224725</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3092949595835319</v>
+        <v>-1.0127425945539748</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04462681205124285</v>
+        <v>0.19765549787519135</v>
       </c>
       <c r="G6" t="n">
-        <v>6.671227395155167E-7</v>
+        <v>1.4027808762309036E-12</v>
       </c>
     </row>
     <row r="7">
@@ -461,19 +461,19 @@
         <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1801278962306344</v>
+        <v>-1.254056622147238</v>
       </c>
       <c r="D7" t="n">
-        <v>0.11353431753020837</v>
+        <v>-1.5809075376718877</v>
       </c>
       <c r="E7" t="n">
-        <v>0.24672147493106045</v>
+        <v>-0.9272057066225883</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03397631566348267</v>
+        <v>0.16676067118604576</v>
       </c>
       <c r="G7" t="n">
-        <v>1.1480952069279173E-7</v>
+        <v>5.4735117808911456E-14</v>
       </c>
     </row>
     <row r="8">
@@ -484,19 +484,19 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>0.22164496416222204</v>
+        <v>-1.3946168092302955</v>
       </c>
       <c r="D8" t="n">
-        <v>0.13406643298069154</v>
+        <v>-1.7784837112112077</v>
       </c>
       <c r="E8" t="n">
-        <v>0.30922349534375254</v>
+        <v>-1.0107499072493833</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04468292407220943</v>
+        <v>0.19585046019434302</v>
       </c>
       <c r="G8" t="n">
-        <v>7.034989066578433E-7</v>
+        <v>1.0728311353881891E-12</v>
       </c>
     </row>
   </sheetData>
@@ -538,19 +538,19 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.4015776287277675</v>
+        <v>0.2214099332546395</v>
       </c>
       <c r="D2" t="n">
-        <v>-1.7501238596949888</v>
+        <v>0.14311121866777887</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.053031397760546</v>
+        <v>0.29970864784150014</v>
       </c>
       <c r="F2" t="n">
-        <v>0.17782970967715372</v>
+        <v>0.03994832376880646</v>
       </c>
       <c r="G2" t="n">
-        <v>3.232882036189485E-15</v>
+        <v>2.983391364305828E-8</v>
       </c>
     </row>
     <row r="3">
@@ -561,19 +561,19 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>-1.6807401761764733</v>
+        <v>0.2822261088617243</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.8861650794791411</v>
+        <v>0.2081560068028972</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.4753152728738055</v>
+        <v>0.35629621092055136</v>
       </c>
       <c r="F3" t="n">
-        <v>0.10480862413401414</v>
+        <v>0.03779086839736076</v>
       </c>
       <c r="G3" t="n">
-        <v>7.130217619944625E-58</v>
+        <v>8.135896837267723E-14</v>
       </c>
     </row>
     <row r="4">
@@ -584,19 +584,19 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>-1.6583639765829643</v>
+        <v>0.2749365150111475</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.16711594055027</v>
+        <v>0.15602066499540998</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.1496120126156586</v>
+        <v>0.39385236502688503</v>
       </c>
       <c r="F4" t="n">
-        <v>0.25956732855474784</v>
+        <v>0.06067135204884568</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6702321788434132E-10</v>
+        <v>5.8546764648028096E-6</v>
       </c>
     </row>
     <row r="5">
@@ -607,19 +607,19 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>-1.1362689954192724</v>
+        <v>0.15467793989100037</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.4682843772107375</v>
+        <v>0.07693060340991685</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8042536136278073</v>
+        <v>0.23242527637208388</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1693956029548291</v>
+        <v>0.039667008408716085</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9760308667197576E-11</v>
+        <v>9.64272646407781E-5</v>
       </c>
     </row>
     <row r="6">
@@ -630,19 +630,19 @@
         <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>-1.4001473703893499</v>
+        <v>0.2218264079630959</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.787552146224725</v>
+        <v>0.13435785634265993</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0127425945539748</v>
+        <v>0.3092949595835319</v>
       </c>
       <c r="F6" t="n">
-        <v>0.19765549787519135</v>
+        <v>0.04462681205124285</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4027808762309036E-12</v>
+        <v>6.671227395155167E-7</v>
       </c>
     </row>
     <row r="7">
@@ -653,19 +653,19 @@
         <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>-1.254056622147238</v>
+        <v>0.1801278962306344</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.5809075376718877</v>
+        <v>0.11353431753020837</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9272057066225883</v>
+        <v>0.24672147493106045</v>
       </c>
       <c r="F7" t="n">
-        <v>0.16676067118604576</v>
+        <v>0.03397631566348267</v>
       </c>
       <c r="G7" t="n">
-        <v>5.4735117808911456E-14</v>
+        <v>1.1480952069279173E-7</v>
       </c>
     </row>
     <row r="8">
@@ -676,19 +676,19 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>-1.3946168092302955</v>
+        <v>0.22164496416222204</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.7784837112112077</v>
+        <v>0.13406643298069154</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0107499072493833</v>
+        <v>0.30922349534375254</v>
       </c>
       <c r="F8" t="n">
-        <v>0.19585046019434302</v>
+        <v>0.04468292407220943</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0728311353881891E-12</v>
+        <v>7.034989066578433E-7</v>
       </c>
     </row>
   </sheetData>
@@ -730,19 +730,19 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1525348127024544</v>
+        <v>0.24660765941256563</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07988008448095689</v>
+        <v>0.16921390221179503</v>
       </c>
       <c r="E2" t="n">
-        <v>0.22518954092395188</v>
+        <v>0.32400141661333626</v>
       </c>
       <c r="F2" t="n">
-        <v>0.03706873888851914</v>
+        <v>0.0394866108167197</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8731745077003464E-5</v>
+        <v>4.228552789830202E-10</v>
       </c>
     </row>
     <row r="3">
@@ -753,19 +753,19 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>0.13787416178828812</v>
+        <v>0.2766374904761365</v>
       </c>
       <c r="D3" t="n">
-        <v>0.047039249526351745</v>
+        <v>0.17881284324130586</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2287090740502245</v>
+        <v>0.37446213771096715</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04634434299078387</v>
+        <v>0.04991053430348503</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0029299387753979403</v>
+        <v>2.978984116750808E-8</v>
       </c>
     </row>
     <row r="4">
@@ -776,19 +776,19 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09918761518299171</v>
+        <v>0.28283726897943673</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.012528714121886553</v>
+        <v>0.16118099852075035</v>
       </c>
       <c r="E4" t="n">
-        <v>0.21090394448786998</v>
+        <v>0.4044935394381231</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05699812719636646</v>
+        <v>0.062069525744227735</v>
       </c>
       <c r="G4" t="n">
-        <v>0.08182552479209777</v>
+        <v>5.194339986901829E-6</v>
       </c>
     </row>
     <row r="5">
@@ -799,19 +799,19 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>0.15027520201066386</v>
+        <v>0.22431520803782024</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05270898089826433</v>
+        <v>0.12140873794895159</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2478414231230634</v>
+        <v>0.3272216781266889</v>
       </c>
       <c r="F5" t="n">
-        <v>0.049778684241020166</v>
+        <v>0.05250330106574931</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002537223123343418</v>
+        <v>1.9337855637200765E-5</v>
       </c>
     </row>
     <row r="6">
@@ -822,19 +822,19 @@
         <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1529189454655285</v>
+        <v>0.24633914912842206</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08020488533450637</v>
+        <v>0.16881113380217153</v>
       </c>
       <c r="E6" t="n">
-        <v>0.22563300559655064</v>
+        <v>0.32386716445467256</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03709901027092966</v>
+        <v>0.03955510986033191</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7573679171046565E-5</v>
+        <v>4.731955381003986E-10</v>
       </c>
     </row>
     <row r="7">
@@ -845,19 +845,19 @@
         <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>0.17597086457732494</v>
+        <v>0.23178300664381848</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0925494638515579</v>
+        <v>0.14383177006066272</v>
       </c>
       <c r="E7" t="n">
-        <v>0.259392265303092</v>
+        <v>0.31973424322697425</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04256193914579951</v>
+        <v>0.044873079889365196</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5578185369765027E-5</v>
+        <v>2.4005109631040167E-7</v>
       </c>
     </row>
     <row r="8">
@@ -868,19 +868,19 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1547665504726187</v>
+        <v>0.24491022426710443</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08187004318057352</v>
+        <v>0.16739911819099118</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2276630577646639</v>
+        <v>0.3224213303432177</v>
       </c>
       <c r="F8" t="n">
-        <v>0.037192095557165905</v>
+        <v>0.039546482691894515</v>
       </c>
       <c r="G8" t="n">
-        <v>3.164752234225635E-5</v>
+        <v>5.90405592526836E-10</v>
       </c>
     </row>
   </sheetData>
@@ -922,19 +922,19 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0145034658338371</v>
+        <v>0.15314889286551586</v>
       </c>
       <c r="D2" t="n">
-        <v>0.005212854420577029</v>
+        <v>0.08021562328183733</v>
       </c>
       <c r="E2" t="n">
-        <v>0.023794077247097173</v>
+        <v>0.22608216244919438</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0047401078639082</v>
+        <v>0.037210851828407415</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0022153417706324337</v>
+        <v>3.859975673701175E-5</v>
       </c>
     </row>
     <row r="3">
@@ -945,19 +945,19 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>0.019360019488255727</v>
+        <v>0.13787416178828812</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007595633701656848</v>
+        <v>0.047039249526351745</v>
       </c>
       <c r="E3" t="n">
-        <v>0.031124405274854605</v>
+        <v>0.2287090740502245</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006002237646223918</v>
+        <v>0.04634434299078387</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0012576733133290135</v>
+        <v>0.0029299387753979403</v>
       </c>
     </row>
     <row r="4">
@@ -968,19 +968,19 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.021051036687392576</v>
+        <v>0.09940528747806154</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006585007038640459</v>
+        <v>-0.012598179333967646</v>
       </c>
       <c r="E4" t="n">
-        <v>0.035517066336144695</v>
+        <v>0.21140875429009073</v>
       </c>
       <c r="F4" t="n">
-        <v>0.007380627371812305</v>
+        <v>0.05714462592450469</v>
       </c>
       <c r="G4" t="n">
-        <v>0.004341756457132125</v>
+        <v>0.08194005363146079</v>
       </c>
     </row>
     <row r="5">
@@ -991,19 +991,19 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>0.010632309428418755</v>
+        <v>0.1515433028216228</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0016483188389578574</v>
+        <v>0.05319942445368979</v>
       </c>
       <c r="E5" t="n">
-        <v>0.022912937695795367</v>
+        <v>0.24988718118955577</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006265626667028884</v>
+        <v>0.05017544814690459</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08971051203184054</v>
+        <v>0.0025255106750274744</v>
       </c>
     </row>
     <row r="6">
@@ -1014,19 +1014,19 @@
         <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>0.014165643121438486</v>
+        <v>0.15353609266003612</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004855664005176017</v>
+        <v>0.08054296044469496</v>
       </c>
       <c r="E6" t="n">
-        <v>0.023475622237700958</v>
+        <v>0.2265292248753773</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0047499893450318725</v>
+        <v>0.037241393987418964</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0028614071651746273</v>
+        <v>3.7441368375322206E-5</v>
       </c>
     </row>
     <row r="7">
@@ -1037,19 +1037,19 @@
         <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>0.011423134114756543</v>
+        <v>0.17711870535326196</v>
       </c>
       <c r="D7" t="n">
-        <v>8.672839773397785E-4</v>
+        <v>0.09324827822426512</v>
       </c>
       <c r="E7" t="n">
-        <v>0.021978984252173307</v>
+        <v>0.2609891324822588</v>
       </c>
       <c r="F7" t="n">
-        <v>0.005385637825212635</v>
+        <v>0.042791034249488186</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03391873544222103</v>
+        <v>3.4858802345521745E-5</v>
       </c>
     </row>
     <row r="8">
@@ -1060,19 +1060,19 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>0.014610727283375412</v>
+        <v>0.15540268423600592</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005301072759873909</v>
+        <v>0.08222474205527015</v>
       </c>
       <c r="E8" t="n">
-        <v>0.023920381806876917</v>
+        <v>0.2285806264167417</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004749823736480359</v>
+        <v>0.03733568478608968</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0020975793007438526</v>
+        <v>3.1504461833923164E-5</v>
       </c>
     </row>
   </sheetData>
@@ -1114,19 +1114,19 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>0.24660765941256563</v>
+        <v>0.0145034658338371</v>
       </c>
       <c r="D2" t="n">
-        <v>0.16921390221179503</v>
+        <v>0.005212854420577029</v>
       </c>
       <c r="E2" t="n">
-        <v>0.32400141661333626</v>
+        <v>0.023794077247097173</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0394866108167197</v>
+        <v>0.0047401078639082</v>
       </c>
       <c r="G2" t="n">
-        <v>4.228552789830202E-10</v>
+        <v>0.0022153417706324337</v>
       </c>
     </row>
     <row r="3">
@@ -1137,19 +1137,19 @@
         <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2766374904761365</v>
+        <v>0.019360019488255727</v>
       </c>
       <c r="D3" t="n">
-        <v>0.17881284324130586</v>
+        <v>0.007595633701656848</v>
       </c>
       <c r="E3" t="n">
-        <v>0.37446213771096715</v>
+        <v>0.031124405274854605</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04991053430348503</v>
+        <v>0.006002237646223918</v>
       </c>
       <c r="G3" t="n">
-        <v>2.978984116750808E-8</v>
+        <v>0.0012576733133290135</v>
       </c>
     </row>
     <row r="4">
@@ -1160,19 +1160,19 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.28283726897943673</v>
+        <v>0.021051036687392576</v>
       </c>
       <c r="D4" t="n">
-        <v>0.16118099852075035</v>
+        <v>0.006585007038640459</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4044935394381231</v>
+        <v>0.035517066336144695</v>
       </c>
       <c r="F4" t="n">
-        <v>0.062069525744227735</v>
+        <v>0.007380627371812305</v>
       </c>
       <c r="G4" t="n">
-        <v>5.194339986901829E-6</v>
+        <v>0.004341756457132125</v>
       </c>
     </row>
     <row r="5">
@@ -1183,19 +1183,19 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>0.22431520803782024</v>
+        <v>0.010632309428418755</v>
       </c>
       <c r="D5" t="n">
-        <v>0.12140873794895159</v>
+        <v>-0.0016483188389578574</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3272216781266889</v>
+        <v>0.022912937695795367</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05250330106574931</v>
+        <v>0.006265626667028884</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9337855637200765E-5</v>
+        <v>0.08971051203184054</v>
       </c>
     </row>
     <row r="6">
@@ -1206,19 +1206,19 @@
         <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>0.24633914912842206</v>
+        <v>0.014165643121438486</v>
       </c>
       <c r="D6" t="n">
-        <v>0.16881113380217153</v>
+        <v>0.004855664005176017</v>
       </c>
       <c r="E6" t="n">
-        <v>0.32386716445467256</v>
+        <v>0.023475622237700958</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03955510986033191</v>
+        <v>0.0047499893450318725</v>
       </c>
       <c r="G6" t="n">
-        <v>4.731955381003986E-10</v>
+        <v>0.0028614071651746273</v>
       </c>
     </row>
     <row r="7">
@@ -1229,19 +1229,19 @@
         <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>0.23178300664381848</v>
+        <v>0.011423134114756543</v>
       </c>
       <c r="D7" t="n">
-        <v>0.14383177006066272</v>
+        <v>8.672839773397785E-4</v>
       </c>
       <c r="E7" t="n">
-        <v>0.31973424322697425</v>
+        <v>0.021978984252173307</v>
       </c>
       <c r="F7" t="n">
-        <v>0.044873079889365196</v>
+        <v>0.005385637825212635</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4005109631040167E-7</v>
+        <v>0.03391873544222103</v>
       </c>
     </row>
     <row r="8">
@@ -1252,19 +1252,19 @@
         <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>0.24491022426710443</v>
+        <v>0.014610727283375412</v>
       </c>
       <c r="D8" t="n">
-        <v>0.16739911819099118</v>
+        <v>0.005301072759873909</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3224213303432177</v>
+        <v>0.023920381806876917</v>
       </c>
       <c r="F8" t="n">
-        <v>0.039546482691894515</v>
+        <v>0.004749823736480359</v>
       </c>
       <c r="G8" t="n">
-        <v>5.90405592526836E-10</v>
+        <v>0.0020975793007438526</v>
       </c>
     </row>
   </sheetData>
@@ -1306,19 +1306,19 @@
         <v>13</v>
       </c>
       <c r="C2" t="n">
-        <v>0.23544755268366943</v>
+        <v>0.23011913258685218</v>
       </c>
       <c r="D2" t="n">
-        <v>0.15400467660878223</v>
+        <v>0.14925497334793525</v>
       </c>
       <c r="E2" t="n">
-        <v>0.31689042875855666</v>
+        <v>0.3109832918257691</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0415524877933098</v>
+        <v>0.04125722410148824</v>
       </c>
       <c r="G2" t="n">
-        <v>1.4594077711538749E-8</v>
+        <v>2.4376317070633728E-8</v>
       </c>
     </row>
     <row r="3">
